--- a/Result/profitability/6988.xlsx
+++ b/Result/profitability/6988.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AM15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2208,6 +2208,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6988</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>191</v>
+      </c>
+      <c r="D15" t="n">
+        <v>137</v>
+      </c>
+      <c r="E15" t="n">
+        <v>53</v>
+      </c>
+      <c r="F15" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-3.44%</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-0.14875</v>
+      </c>
+      <c r="N15" t="n">
+        <v>28.2175</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.09999999999999999</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-3.220000000000002</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0.1032382173773646</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>-0.5161290322580645</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.2200000000000024</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0.007804185881518322</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
